--- a/TruScore logic/PLANET Pillar.xlsx
+++ b/TruScore logic/PLANET Pillar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TrueScan-FoodScanner\TruScore logic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1C89180-3072-4F03-B0E1-B4786C55901A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B889F880-9B5F-407E-B807-DA5576089C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D187179-B174-44E8-9D97-B1365510EBF5}"/>
+    <workbookView xWindow="33735" yWindow="750" windowWidth="23055" windowHeight="14730" xr2:uid="{3D187179-B174-44E8-9D97-B1365510EBF5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -96,9 +96,6 @@
     <t xml:space="preserve"> ecoscore_grade (string a-e) or CSV lookups (e.g., carbon factors) </t>
   </si>
   <si>
-    <t xml:space="preserve"> A=+10, B=+5, C=0, D=-5, E=-10 (adj base, direct map); high CSV carbon=-5 if OFF missing </t>
-  </si>
-  <si>
     <t xml:space="preserve"> Official FR system (G20 push); ADEME LCA cuts emissions 50% for A. CSVs supplement for coverage\'97public grades defend. </t>
   </si>
   <si>
@@ -120,9 +117,6 @@
     <t xml:space="preserve"> palm_oil (boolean or tags) </t>
   </si>
   <si>
-    <t xml:space="preserve"> Non-sust palm=-8; sustainable/cert RSPO=0; brand/parent low WWF/RSPO=-5 overlay (even on clean products\'97accountability) </t>
-  </si>
-  <si>
     <t xml:space="preserve"> WWF studies defend; Brand data reliable (53% global volume)\'97penalize parents for virality. Neutral 0 for cert rewards good actors without over-bonus (greenwashing risk). </t>
   </si>
   <si>
@@ -144,9 +138,6 @@
     <t xml:space="preserve"> packaging_tags (recycling array) </t>
   </si>
   <si>
-    <t xml:space="preserve"> Full recycle (local laws)=+5, partial=+2; high eco-cost material=-5 </t>
-  </si>
-  <si>
     <t xml:space="preserve"> EPA studies defend; Idemat eco-costs reliable. Public grades defend\'97penalize parents if material from shady supply. Local geo via ECR/ReCoRe CSVs (country/material recyclable per laws)\'97defensible public. </t>
   </si>
   <si>
@@ -190,6 +181,15 @@
   </si>
   <si>
     <t xml:space="preserve"> 1. Applied after all adjustments; overrides if &lt;0. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A=+7, B=+3, C=0, D=--3, E=--7 (adj base, direct map); high CSV carbon=-5 if OFF missing </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Non-sust palm=-8; sustainable/cert RSPO=0; brand/parent low WWF/RSPO=-4 overlay (even on clean products\'97accountability) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Full recycle (local laws)=+3, partial=+1; high eco-cost material=-6 </t>
   </si>
 </sst>
 </file>
@@ -664,100 +664,100 @@
         <v>22</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="102" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="G5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="129.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>14</v>
@@ -766,19 +766,19 @@
         <v>12</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
